--- a/www/flightdata/xlsx/eoss-330.xlsx
+++ b/www/flightdata/xlsx/eoss-330.xlsx
@@ -3339,7 +3339,7 @@
         <v>31058.82</v>
       </c>
       <c r="I2">
-        <v>564</v>
+        <v>420</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
